--- a/project-a/tables/excel/monster_ai/MonsterAITables.xlsx
+++ b/project-a/tables/excel/monster_ai/MonsterAITables.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_monsters" sheetId="1" r:id="Rc479f552906f4277"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_stats" sheetId="2" r:id="R9136eea5e7ca4fd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_actions" sheetId="3" r:id="R386f681b84314d9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_patterns" sheetId="4" r:id="R2e395eea77e14d7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_encounters" sheetId="5" r:id="R74c4e103cb3a49d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_rules" sheetId="6" r:id="R9da3593aa0764d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_monsters" sheetId="1" r:id="Ra0af4039672143a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_stats" sheetId="2" r:id="Rc42263fb94424c79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_actions" sheetId="3" r:id="Rd2ead83e3f134793"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_patterns" sheetId="4" r:id="Rb9b4e92ebe4e4349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_encounters" sheetId="5" r:id="R31eb5eb9f05744e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_ai_rules" sheetId="6" r:id="R7993979a936c4143"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -216,7 +216,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="56">
+  <x:cellXfs count="60">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -335,7 +335,22 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -350,7 +365,23 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -585,16 +616,16 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="62" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="48" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="58" hidden="0" customWidth="1"/>
     <x:col min="1" max="1" width="4" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -742,40 +773,205 @@
         <x:v>-48</x:v>
       </x:c>
       <x:c r="K5" s="46" t="str">
-        <x:v>기본 온보딩 몬스터. 인카운터 시작 위치에 따라 공격/방어 예고가 갈린다.</x:v>
+        <x:v>예고 읽기와 개체별 시작 행동을 가르치는 온보딩 몬스터.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="42"/>
-      <x:c r="B6" s="50" t="str">
+      <x:c r="A6" s="39"/>
+      <x:c r="B6" s="49" t="str">
+        <x:v>bog_stalker</x:v>
+      </x:c>
+      <x:c r="C6" s="45" t="str">
+        <x:v>늪 추적자</x:v>
+      </x:c>
+      <x:c r="D6" s="45" t="str">
+        <x:v>bog_stalker</x:v>
+      </x:c>
+      <x:c r="E6" s="45" t="str">
+        <x:v>bog_stalker_basic</x:v>
+      </x:c>
+      <x:c r="F6" s="45" t="str">
+        <x:v>res://scenes/monster/monster_bog_stalker.tscn</x:v>
+      </x:c>
+      <x:c r="G6" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="45" t="n">
+        <x:v>-172</x:v>
+      </x:c>
+      <x:c r="I6" s="45" t="n">
+        <x:v>-14</x:v>
+      </x:c>
+      <x:c r="J6" s="45" t="n">
+        <x:v>-48</x:v>
+      </x:c>
+      <x:c r="K6" s="46" t="str">
+        <x:v>짧은 행동 카운트로 카드 사용량을 압박하는 초반 몬스터.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="39"/>
+      <x:c r="B7" s="49" t="str">
+        <x:v>bone_crawler</x:v>
+      </x:c>
+      <x:c r="C7" s="45" t="str">
+        <x:v>뼈 크롤러</x:v>
+      </x:c>
+      <x:c r="D7" s="45" t="str">
+        <x:v>bone_crawler</x:v>
+      </x:c>
+      <x:c r="E7" s="45" t="str">
+        <x:v>bone_crawler_basic</x:v>
+      </x:c>
+      <x:c r="F7" s="45" t="str">
+        <x:v>res://scenes/monster/monster_bone_crawler.tscn</x:v>
+      </x:c>
+      <x:c r="G7" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="45" t="n">
+        <x:v>-172</x:v>
+      </x:c>
+      <x:c r="I7" s="45" t="n">
+        <x:v>-14</x:v>
+      </x:c>
+      <x:c r="J7" s="45" t="n">
+        <x:v>-48</x:v>
+      </x:c>
+      <x:c r="K7" s="46" t="str">
+        <x:v>강한 선공 예고 뒤 빈틈을 주는 위험 몬스터.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="39"/>
+      <x:c r="B8" s="49" t="str">
+        <x:v>gravebound_crawler</x:v>
+      </x:c>
+      <x:c r="C8" s="45" t="str">
+        <x:v>무덤 크롤러</x:v>
+      </x:c>
+      <x:c r="D8" s="45" t="str">
+        <x:v>gravebound_crawler</x:v>
+      </x:c>
+      <x:c r="E8" s="45" t="str">
+        <x:v>gravebound_crawler_basic</x:v>
+      </x:c>
+      <x:c r="F8" s="45" t="str">
+        <x:v>res://scenes/monster/monster_gravebound_crawler.tscn</x:v>
+      </x:c>
+      <x:c r="G8" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="45" t="n">
+        <x:v>-172</x:v>
+      </x:c>
+      <x:c r="I8" s="45" t="n">
+        <x:v>-14</x:v>
+      </x:c>
+      <x:c r="J8" s="45" t="n">
+        <x:v>-48</x:v>
+      </x:c>
+      <x:c r="K8" s="46" t="str">
+        <x:v>방어 누적과 장기전 돌파를 요구하는 몬스터.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="39"/>
+      <x:c r="B9" s="49" t="str">
         <x:v>frost_revenant</x:v>
       </x:c>
-      <x:c r="C6" s="47" t="str">
+      <x:c r="C9" s="45" t="str">
         <x:v>프로스트 레버넌트</x:v>
       </x:c>
-      <x:c r="D6" s="47" t="str">
+      <x:c r="D9" s="45" t="str">
         <x:v>frost_revenant</x:v>
       </x:c>
-      <x:c r="E6" s="47" t="str">
+      <x:c r="E9" s="45" t="str">
         <x:v>frost_revenant_basic</x:v>
       </x:c>
-      <x:c r="F6" s="47" t="str">
+      <x:c r="F9" s="45" t="str">
         <x:v>res://scenes/monster/monster_frost_revenant.tscn</x:v>
       </x:c>
-      <x:c r="G6" s="47" t="n">
+      <x:c r="G9" s="45" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H6" s="47" t="n">
+      <x:c r="H9" s="45" t="n">
         <x:v>-172</x:v>
       </x:c>
-      <x:c r="I6" s="47" t="n">
+      <x:c r="I9" s="45" t="n">
         <x:v>-14</x:v>
       </x:c>
-      <x:c r="J6" s="47" t="n">
+      <x:c r="J9" s="45" t="n">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="K6" s="48" t="str">
-        <x:v>버프 후 공격과 방어를 반복하는 엘리트 후보.</x:v>
+      <x:c r="K9" s="46" t="str">
+        <x:v>버프-공격-방어 주기를 읽게 하는 엘리트형 몬스터.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="39"/>
+      <x:c r="B10" s="49" t="str">
+        <x:v>crown_acolyte</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="str">
+        <x:v>왕관 시종</x:v>
+      </x:c>
+      <x:c r="D10" s="45" t="str">
+        <x:v>crown_acolyte</x:v>
+      </x:c>
+      <x:c r="E10" s="45" t="str">
+        <x:v>crown_acolyte_basic</x:v>
+      </x:c>
+      <x:c r="F10" s="45" t="str">
+        <x:v>res://scenes/monster/monster_crown_acolyte.tscn</x:v>
+      </x:c>
+      <x:c r="G10" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="45" t="n">
+        <x:v>-172</x:v>
+      </x:c>
+      <x:c r="I10" s="45" t="n">
+        <x:v>-14</x:v>
+      </x:c>
+      <x:c r="J10" s="45" t="n">
+        <x:v>-48</x:v>
+      </x:c>
+      <x:c r="K10" s="46" t="str">
+        <x:v>단죄 전조와 고압박 공격으로 위험 턴을 예측하게 하는 몬스터.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="42"/>
+      <x:c r="B11" s="50" t="str">
+        <x:v>abyssal_crown_guardian</x:v>
+      </x:c>
+      <x:c r="C11" s="47" t="str">
+        <x:v>심연 왕관 수호자</x:v>
+      </x:c>
+      <x:c r="D11" s="47" t="str">
+        <x:v>abyssal_crown_guardian</x:v>
+      </x:c>
+      <x:c r="E11" s="47" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="F11" s="47" t="str">
+        <x:v>res://scenes/monster/monster_abyssal_crown_guardian.tscn</x:v>
+      </x:c>
+      <x:c r="G11" s="47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="47" t="n">
+        <x:v>-172</x:v>
+      </x:c>
+      <x:c r="I11" s="47" t="n">
+        <x:v>-14</x:v>
+      </x:c>
+      <x:c r="J11" s="47" t="n">
+        <x:v>-48</x:v>
+      </x:c>
+      <x:c r="K11" s="48" t="str">
+        <x:v>큰 전조 후 강공격을 사용하는 보스 몬스터.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -787,11 +983,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="52" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
     <x:col min="1" max="1" width="4" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -874,25 +1070,115 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F5" s="46" t="str">
-        <x:v>attack/defense는 행동 power_type 계산의 기준값.</x:v>
+        <x:v>낮은 방어로 학습용 방어 행동 제공.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="42"/>
-      <x:c r="B6" s="50" t="str">
+      <x:c r="A6" s="39"/>
+      <x:c r="B6" s="49" t="str">
+        <x:v>bog_stalker</x:v>
+      </x:c>
+      <x:c r="C6" s="45" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="D6" s="45" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E6" s="45" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="46" t="str">
+        <x:v>회피/독성 느낌의 얕은 방어.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="39"/>
+      <x:c r="B7" s="49" t="str">
+        <x:v>bone_crawler</x:v>
+      </x:c>
+      <x:c r="C7" s="45" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="D7" s="45" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E7" s="45" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F7" s="46" t="str">
+        <x:v>선공 후 뼈를 추스르는 방어.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="39"/>
+      <x:c r="B8" s="49" t="str">
+        <x:v>gravebound_crawler</x:v>
+      </x:c>
+      <x:c r="C8" s="45" t="n">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="D8" s="45" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E8" s="45" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F8" s="46" t="str">
+        <x:v>장기전 정체성 강화.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="39"/>
+      <x:c r="B9" s="49" t="str">
         <x:v>frost_revenant</x:v>
       </x:c>
-      <x:c r="C6" s="47" t="n">
+      <x:c r="C9" s="45" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="D6" s="47" t="n">
+      <x:c r="D9" s="45" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E6" s="47" t="n">
+      <x:c r="E9" s="45" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F6" s="48" t="str">
-        <x:v>얼음 갑옷은 defense_percent 기반으로 조정한다.</x:v>
+      <x:c r="F9" s="46" t="str">
+        <x:v>얼음 갑옷을 의미 있게 만들기.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="39"/>
+      <x:c r="B10" s="49" t="str">
+        <x:v>crown_acolyte</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="n">
+        <x:v>1400</x:v>
+      </x:c>
+      <x:c r="D10" s="45" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="45" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F10" s="46" t="str">
+        <x:v>공격형이지만 신앙 보호막 보유.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="42"/>
+      <x:c r="B11" s="50" t="str">
+        <x:v>abyssal_crown_guardian</x:v>
+      </x:c>
+      <x:c r="C11" s="47" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="D11" s="47" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E11" s="47" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F11" s="48" t="str">
+        <x:v>보스의 패턴 방어 기준.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -904,14 +1190,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="52" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="58" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
     <x:col min="1" max="1" width="4" hidden="0" customWidth="1"/>
@@ -1063,28 +1349,28 @@
     <x:row r="6">
       <x:c r="A6" s="39"/>
       <x:c r="B6" s="49" t="str">
-        <x:v>mire_imp_guard</x:v>
+        <x:v>mire_imp_flurry</x:v>
       </x:c>
       <x:c r="C6" s="45" t="str">
-        <x:v>방어</x:v>
+        <x:v>마구 휘두르기</x:v>
       </x:c>
       <x:c r="D6" s="45" t="str">
-        <x:v>defense</x:v>
+        <x:v>attack</x:v>
       </x:c>
       <x:c r="E6" s="45" t="str">
-        <x:v>self</x:v>
+        <x:v>player</x:v>
       </x:c>
       <x:c r="F6" s="45" t="str">
-        <x:v>defense_percent</x:v>
+        <x:v>attack_percent</x:v>
       </x:c>
       <x:c r="G6" s="45" t="n">
-        <x:v>100</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H6" s="45" t="str">
-        <x:v>DEF</x:v>
+        <x:v>ATK</x:v>
       </x:c>
       <x:c r="I6" s="45" t="str">
-        <x:v>자신에게 defense의 100% 실드를 부여한다.</x:v>
+        <x:v>대상에게 attack의 140% 피해를 준다.</x:v>
       </x:c>
       <x:c r="J6" s="45"/>
       <x:c r="K6" s="46"/>
@@ -1092,28 +1378,28 @@
     <x:row r="7">
       <x:c r="A7" s="39"/>
       <x:c r="B7" s="49" t="str">
-        <x:v>frost_morale</x:v>
+        <x:v>mire_imp_crouch</x:v>
       </x:c>
       <x:c r="C7" s="45" t="str">
-        <x:v>사기</x:v>
+        <x:v>웅크리기</x:v>
       </x:c>
       <x:c r="D7" s="45" t="str">
-        <x:v>buff</x:v>
+        <x:v>defense</x:v>
       </x:c>
       <x:c r="E7" s="45" t="str">
         <x:v>self</x:v>
       </x:c>
       <x:c r="F7" s="45" t="str">
-        <x:v>flat</x:v>
+        <x:v>defense_percent</x:v>
       </x:c>
       <x:c r="G7" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H7" s="45" t="str">
-        <x:v>BUF</x:v>
+        <x:v>DEF</x:v>
       </x:c>
       <x:c r="I7" s="45" t="str">
-        <x:v>자신에게 사기 1을 부여한다.</x:v>
+        <x:v>자신에게 defense의 100% 실드를 부여한다.</x:v>
       </x:c>
       <x:c r="J7" s="45"/>
       <x:c r="K7" s="46"/>
@@ -1121,60 +1407,843 @@
     <x:row r="8">
       <x:c r="A8" s="39"/>
       <x:c r="B8" s="49" t="str">
-        <x:v>frost_ice_blade</x:v>
+        <x:v>mire_imp_giggle</x:v>
       </x:c>
       <x:c r="C8" s="45" t="str">
-        <x:v>얼음 칼날</x:v>
+        <x:v>낄낄대기</x:v>
       </x:c>
       <x:c r="D8" s="45" t="str">
-        <x:v>attack</x:v>
+        <x:v>skill</x:v>
       </x:c>
       <x:c r="E8" s="45" t="str">
-        <x:v>player</x:v>
+        <x:v>self</x:v>
       </x:c>
       <x:c r="F8" s="45" t="str">
-        <x:v>attack_percent</x:v>
+        <x:v>count_delta</x:v>
       </x:c>
       <x:c r="G8" s="45" t="n">
-        <x:v>130</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="H8" s="45" t="str">
-        <x:v>ATK</x:v>
+        <x:v>SKL</x:v>
       </x:c>
       <x:c r="I8" s="45" t="str">
-        <x:v>대상에게 attack의 130% 피해를 준다.</x:v>
+        <x:v>다음 자신의 행동 카운트를 1 감소시킨다.</x:v>
       </x:c>
       <x:c r="J8" s="45"/>
       <x:c r="K8" s="46"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="42"/>
-      <x:c r="B9" s="50" t="str">
+      <x:c r="A9" s="39"/>
+      <x:c r="B9" s="49" t="str">
+        <x:v>bog_stalker_stab</x:v>
+      </x:c>
+      <x:c r="C9" s="45" t="str">
+        <x:v>찌르기</x:v>
+      </x:c>
+      <x:c r="D9" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E9" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F9" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G9" s="45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H9" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I9" s="45" t="str">
+        <x:v>대상에게 attack의 100% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J9" s="45"/>
+      <x:c r="K9" s="46"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="39"/>
+      <x:c r="B10" s="49" t="str">
+        <x:v>bog_stalker_ambush</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="str">
+        <x:v>잠복 기습</x:v>
+      </x:c>
+      <x:c r="D10" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E10" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F10" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G10" s="45" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H10" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I10" s="45" t="str">
+        <x:v>대상에게 attack의 130% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J10" s="45"/>
+      <x:c r="K10" s="46"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="39"/>
+      <x:c r="B11" s="49" t="str">
+        <x:v>bog_stalker_mud_cover</x:v>
+      </x:c>
+      <x:c r="C11" s="45" t="str">
+        <x:v>진흙 엄폐</x:v>
+      </x:c>
+      <x:c r="D11" s="45" t="str">
+        <x:v>defense</x:v>
+      </x:c>
+      <x:c r="E11" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F11" s="45" t="str">
+        <x:v>defense_percent</x:v>
+      </x:c>
+      <x:c r="G11" s="45" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H11" s="45" t="str">
+        <x:v>DEF</x:v>
+      </x:c>
+      <x:c r="I11" s="45" t="str">
+        <x:v>자신에게 defense의 80% 실드를 부여한다.</x:v>
+      </x:c>
+      <x:c r="J11" s="45"/>
+      <x:c r="K11" s="46"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="39"/>
+      <x:c r="B12" s="49" t="str">
+        <x:v>bog_stalker_venom</x:v>
+      </x:c>
+      <x:c r="C12" s="45" t="str">
+        <x:v>늪독 바르기</x:v>
+      </x:c>
+      <x:c r="D12" s="45" t="str">
+        <x:v>buff</x:v>
+      </x:c>
+      <x:c r="E12" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F12" s="45" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="G12" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="45" t="str">
+        <x:v>BUF</x:v>
+      </x:c>
+      <x:c r="I12" s="45" t="str">
+        <x:v>다음 공격 피해를 강화한다.</x:v>
+      </x:c>
+      <x:c r="J12" s="45"/>
+      <x:c r="K12" s="46"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="39"/>
+      <x:c r="B13" s="49" t="str">
+        <x:v>bone_crawler_claw</x:v>
+      </x:c>
+      <x:c r="C13" s="45" t="str">
+        <x:v>뼈 할퀴기</x:v>
+      </x:c>
+      <x:c r="D13" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E13" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F13" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G13" s="45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H13" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I13" s="45" t="str">
+        <x:v>대상에게 attack의 100% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J13" s="45"/>
+      <x:c r="K13" s="46"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="39"/>
+      <x:c r="B14" s="49" t="str">
+        <x:v>bone_crawler_skull_slam</x:v>
+      </x:c>
+      <x:c r="C14" s="45" t="str">
+        <x:v>해골 강타</x:v>
+      </x:c>
+      <x:c r="D14" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E14" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F14" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G14" s="45" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H14" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I14" s="45" t="str">
+        <x:v>대상에게 attack의 150% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J14" s="45"/>
+      <x:c r="K14" s="46"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="39"/>
+      <x:c r="B15" s="49" t="str">
+        <x:v>bone_crawler_reassemble</x:v>
+      </x:c>
+      <x:c r="C15" s="45" t="str">
+        <x:v>뼈 재조립</x:v>
+      </x:c>
+      <x:c r="D15" s="45" t="str">
+        <x:v>defense</x:v>
+      </x:c>
+      <x:c r="E15" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F15" s="45" t="str">
+        <x:v>defense_percent</x:v>
+      </x:c>
+      <x:c r="G15" s="45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H15" s="45" t="str">
+        <x:v>DEF</x:v>
+      </x:c>
+      <x:c r="I15" s="45" t="str">
+        <x:v>자신에게 defense의 100% 실드를 부여한다.</x:v>
+      </x:c>
+      <x:c r="J15" s="45"/>
+      <x:c r="K15" s="46"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="39"/>
+      <x:c r="B16" s="49" t="str">
+        <x:v>bone_crawler_cracked_bone</x:v>
+      </x:c>
+      <x:c r="C16" s="45" t="str">
+        <x:v>금 간 뼈</x:v>
+      </x:c>
+      <x:c r="D16" s="45" t="str">
+        <x:v>buff</x:v>
+      </x:c>
+      <x:c r="E16" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F16" s="45" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="G16" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="45" t="str">
+        <x:v>BUF</x:v>
+      </x:c>
+      <x:c r="I16" s="45" t="str">
+        <x:v>자신을 정비하고 다음 공격 피해를 소폭 강화한다.</x:v>
+      </x:c>
+      <x:c r="J16" s="45"/>
+      <x:c r="K16" s="46"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="39"/>
+      <x:c r="B17" s="49" t="str">
+        <x:v>gravebound_bite</x:v>
+      </x:c>
+      <x:c r="C17" s="45" t="str">
+        <x:v>묘지 물어뜯기</x:v>
+      </x:c>
+      <x:c r="D17" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E17" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F17" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G17" s="45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H17" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I17" s="45" t="str">
+        <x:v>대상에게 attack의 100% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J17" s="45"/>
+      <x:c r="K17" s="46"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="39"/>
+      <x:c r="B18" s="49" t="str">
+        <x:v>gravebound_jaw</x:v>
+      </x:c>
+      <x:c r="C18" s="45" t="str">
+        <x:v>매장자의 턱</x:v>
+      </x:c>
+      <x:c r="D18" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E18" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F18" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G18" s="45" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H18" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I18" s="45" t="str">
+        <x:v>대상에게 attack의 140% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J18" s="45"/>
+      <x:c r="K18" s="46"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="39"/>
+      <x:c r="B19" s="49" t="str">
+        <x:v>gravebound_earth_armor</x:v>
+      </x:c>
+      <x:c r="C19" s="45" t="str">
+        <x:v>흙무덤 장갑</x:v>
+      </x:c>
+      <x:c r="D19" s="45" t="str">
+        <x:v>defense</x:v>
+      </x:c>
+      <x:c r="E19" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F19" s="45" t="str">
+        <x:v>defense_percent</x:v>
+      </x:c>
+      <x:c r="G19" s="45" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H19" s="45" t="str">
+        <x:v>DEF</x:v>
+      </x:c>
+      <x:c r="I19" s="45" t="str">
+        <x:v>자신에게 defense의 150% 실드를 부여한다.</x:v>
+      </x:c>
+      <x:c r="J19" s="45"/>
+      <x:c r="K19" s="46"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="39"/>
+      <x:c r="B20" s="49" t="str">
+        <x:v>gravebound_hard_bones</x:v>
+      </x:c>
+      <x:c r="C20" s="45" t="str">
+        <x:v>망자의 강골</x:v>
+      </x:c>
+      <x:c r="D20" s="45" t="str">
+        <x:v>buff</x:v>
+      </x:c>
+      <x:c r="E20" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F20" s="45" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="G20" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="45" t="str">
+        <x:v>BUF</x:v>
+      </x:c>
+      <x:c r="I20" s="45" t="str">
+        <x:v>자신을 단단히 굳혀 다음 공격 피해를 소폭 강화한다.</x:v>
+      </x:c>
+      <x:c r="J20" s="45"/>
+      <x:c r="K20" s="46"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="39"/>
+      <x:c r="B21" s="49" t="str">
+        <x:v>frost_ice_blade</x:v>
+      </x:c>
+      <x:c r="C21" s="45" t="str">
+        <x:v>얼음 칼날</x:v>
+      </x:c>
+      <x:c r="D21" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E21" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F21" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G21" s="45" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H21" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I21" s="45" t="str">
+        <x:v>대상에게 attack의 130% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J21" s="45"/>
+      <x:c r="K21" s="46"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="39"/>
+      <x:c r="B22" s="49" t="str">
+        <x:v>frost_cleave</x:v>
+      </x:c>
+      <x:c r="C22" s="45" t="str">
+        <x:v>서리 절단</x:v>
+      </x:c>
+      <x:c r="D22" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E22" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F22" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G22" s="45" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H22" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I22" s="45" t="str">
+        <x:v>대상에게 attack의 170% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J22" s="45"/>
+      <x:c r="K22" s="46"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="39"/>
+      <x:c r="B23" s="49" t="str">
         <x:v>frost_ice_armor</x:v>
       </x:c>
-      <x:c r="C9" s="47" t="str">
+      <x:c r="C23" s="45" t="str">
         <x:v>얼음 갑옷</x:v>
       </x:c>
-      <x:c r="D9" s="47" t="str">
+      <x:c r="D23" s="45" t="str">
         <x:v>defense</x:v>
       </x:c>
-      <x:c r="E9" s="47" t="str">
+      <x:c r="E23" s="45" t="str">
         <x:v>self</x:v>
       </x:c>
-      <x:c r="F9" s="47" t="str">
+      <x:c r="F23" s="45" t="str">
         <x:v>defense_percent</x:v>
       </x:c>
-      <x:c r="G9" s="47" t="n">
+      <x:c r="G23" s="45" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H9" s="47" t="str">
+      <x:c r="H23" s="45" t="str">
         <x:v>DEF</x:v>
       </x:c>
-      <x:c r="I9" s="47" t="str">
+      <x:c r="I23" s="45" t="str">
         <x:v>자신에게 defense의 150% 실드를 부여한다.</x:v>
       </x:c>
-      <x:c r="J9" s="47"/>
-      <x:c r="K9" s="48"/>
+      <x:c r="J23" s="45"/>
+      <x:c r="K23" s="46"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="39"/>
+      <x:c r="B24" s="49" t="str">
+        <x:v>frost_morale</x:v>
+      </x:c>
+      <x:c r="C24" s="45" t="str">
+        <x:v>사기</x:v>
+      </x:c>
+      <x:c r="D24" s="45" t="str">
+        <x:v>buff</x:v>
+      </x:c>
+      <x:c r="E24" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F24" s="45" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="G24" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="45" t="str">
+        <x:v>BUF</x:v>
+      </x:c>
+      <x:c r="I24" s="45" t="str">
+        <x:v>다음 공격 피해를 강화한다.</x:v>
+      </x:c>
+      <x:c r="J24" s="45"/>
+      <x:c r="K24" s="46"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="39"/>
+      <x:c r="B25" s="49" t="str">
+        <x:v>frost_mark</x:v>
+      </x:c>
+      <x:c r="C25" s="45" t="str">
+        <x:v>빙결 표식</x:v>
+      </x:c>
+      <x:c r="D25" s="45" t="str">
+        <x:v>skill</x:v>
+      </x:c>
+      <x:c r="E25" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F25" s="45" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="G25" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H25" s="45" t="str">
+        <x:v>SKL</x:v>
+      </x:c>
+      <x:c r="I25" s="45" t="str">
+        <x:v>플레이어를 압박하는 빙결 표식을 예고한다.</x:v>
+      </x:c>
+      <x:c r="J25" s="45"/>
+      <x:c r="K25" s="46"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="39"/>
+      <x:c r="B26" s="49" t="str">
+        <x:v>crown_staff</x:v>
+      </x:c>
+      <x:c r="C26" s="45" t="str">
+        <x:v>단죄의 지팡이</x:v>
+      </x:c>
+      <x:c r="D26" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E26" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F26" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G26" s="45" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H26" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I26" s="45" t="str">
+        <x:v>대상에게 attack의 130% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J26" s="45"/>
+      <x:c r="K26" s="46"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="39"/>
+      <x:c r="B27" s="49" t="str">
+        <x:v>crown_judgement</x:v>
+      </x:c>
+      <x:c r="C27" s="45" t="str">
+        <x:v>심판의 일격</x:v>
+      </x:c>
+      <x:c r="D27" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E27" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F27" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G27" s="45" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H27" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I27" s="45" t="str">
+        <x:v>대상에게 attack의 180% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J27" s="45"/>
+      <x:c r="K27" s="46"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="39"/>
+      <x:c r="B28" s="49" t="str">
+        <x:v>crown_veil</x:v>
+      </x:c>
+      <x:c r="C28" s="45" t="str">
+        <x:v>신앙의 장막</x:v>
+      </x:c>
+      <x:c r="D28" s="45" t="str">
+        <x:v>defense</x:v>
+      </x:c>
+      <x:c r="E28" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F28" s="45" t="str">
+        <x:v>defense_percent</x:v>
+      </x:c>
+      <x:c r="G28" s="45" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H28" s="45" t="str">
+        <x:v>DEF</x:v>
+      </x:c>
+      <x:c r="I28" s="45" t="str">
+        <x:v>자신에게 defense의 120% 실드를 부여한다.</x:v>
+      </x:c>
+      <x:c r="J28" s="45"/>
+      <x:c r="K28" s="46"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="39"/>
+      <x:c r="B29" s="49" t="str">
+        <x:v>crown_sentence</x:v>
+      </x:c>
+      <x:c r="C29" s="45" t="str">
+        <x:v>단죄 선포</x:v>
+      </x:c>
+      <x:c r="D29" s="45" t="str">
+        <x:v>skill</x:v>
+      </x:c>
+      <x:c r="E29" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F29" s="45" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="G29" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="45" t="str">
+        <x:v>SKL</x:v>
+      </x:c>
+      <x:c r="I29" s="45" t="str">
+        <x:v>심판의 전조를 남긴다.</x:v>
+      </x:c>
+      <x:c r="J29" s="45"/>
+      <x:c r="K29" s="46"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="39"/>
+      <x:c r="B30" s="49" t="str">
+        <x:v>crown_deep_faith</x:v>
+      </x:c>
+      <x:c r="C30" s="45" t="str">
+        <x:v>깊은 신앙</x:v>
+      </x:c>
+      <x:c r="D30" s="45" t="str">
+        <x:v>buff</x:v>
+      </x:c>
+      <x:c r="E30" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F30" s="45" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="G30" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="45" t="str">
+        <x:v>BUF</x:v>
+      </x:c>
+      <x:c r="I30" s="45" t="str">
+        <x:v>다음 공격 피해를 강화한다.</x:v>
+      </x:c>
+      <x:c r="J30" s="45"/>
+      <x:c r="K30" s="46"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="39"/>
+      <x:c r="B31" s="49" t="str">
+        <x:v>guardian_crush</x:v>
+      </x:c>
+      <x:c r="C31" s="45" t="str">
+        <x:v>왕관 분쇄</x:v>
+      </x:c>
+      <x:c r="D31" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E31" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F31" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G31" s="45" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H31" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I31" s="45" t="str">
+        <x:v>대상에게 attack의 150% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J31" s="45"/>
+      <x:c r="K31" s="46"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="39"/>
+      <x:c r="B32" s="49" t="str">
+        <x:v>guardian_edict</x:v>
+      </x:c>
+      <x:c r="C32" s="45" t="str">
+        <x:v>심연의 칙령</x:v>
+      </x:c>
+      <x:c r="D32" s="45" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="E32" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F32" s="45" t="str">
+        <x:v>attack_percent</x:v>
+      </x:c>
+      <x:c r="G32" s="45" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H32" s="45" t="str">
+        <x:v>ATK</x:v>
+      </x:c>
+      <x:c r="I32" s="45" t="str">
+        <x:v>대상에게 attack의 200% 피해를 준다.</x:v>
+      </x:c>
+      <x:c r="J32" s="45"/>
+      <x:c r="K32" s="46"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="39"/>
+      <x:c r="B33" s="49" t="str">
+        <x:v>guardian_barrier</x:v>
+      </x:c>
+      <x:c r="C33" s="45" t="str">
+        <x:v>왕관 방벽</x:v>
+      </x:c>
+      <x:c r="D33" s="45" t="str">
+        <x:v>defense</x:v>
+      </x:c>
+      <x:c r="E33" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F33" s="45" t="str">
+        <x:v>defense_percent</x:v>
+      </x:c>
+      <x:c r="G33" s="45" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H33" s="45" t="str">
+        <x:v>DEF</x:v>
+      </x:c>
+      <x:c r="I33" s="45" t="str">
+        <x:v>자신에게 defense의 160% 실드를 부여한다.</x:v>
+      </x:c>
+      <x:c r="J33" s="45"/>
+      <x:c r="K33" s="46"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="39"/>
+      <x:c r="B34" s="49" t="str">
+        <x:v>guardian_deep_guard</x:v>
+      </x:c>
+      <x:c r="C34" s="45" t="str">
+        <x:v>심연 수호</x:v>
+      </x:c>
+      <x:c r="D34" s="45" t="str">
+        <x:v>defense</x:v>
+      </x:c>
+      <x:c r="E34" s="45" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F34" s="45" t="str">
+        <x:v>defense_percent</x:v>
+      </x:c>
+      <x:c r="G34" s="45" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H34" s="45" t="str">
+        <x:v>DEF</x:v>
+      </x:c>
+      <x:c r="I34" s="45" t="str">
+        <x:v>자신에게 defense의 120% 실드를 부여한다.</x:v>
+      </x:c>
+      <x:c r="J34" s="45"/>
+      <x:c r="K34" s="46"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="39"/>
+      <x:c r="B35" s="49" t="str">
+        <x:v>guardian_sentence</x:v>
+      </x:c>
+      <x:c r="C35" s="45" t="str">
+        <x:v>심연 선고</x:v>
+      </x:c>
+      <x:c r="D35" s="45" t="str">
+        <x:v>skill</x:v>
+      </x:c>
+      <x:c r="E35" s="45" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="F35" s="45" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="G35" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" s="45" t="str">
+        <x:v>SKL</x:v>
+      </x:c>
+      <x:c r="I35" s="45" t="str">
+        <x:v>강력한 보스 패턴의 전조를 남긴다.</x:v>
+      </x:c>
+      <x:c r="J35" s="45"/>
+      <x:c r="K35" s="46"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="42"/>
+      <x:c r="B36" s="50" t="str">
+        <x:v>guardian_authority</x:v>
+      </x:c>
+      <x:c r="C36" s="47" t="str">
+        <x:v>왕관의 권능</x:v>
+      </x:c>
+      <x:c r="D36" s="47" t="str">
+        <x:v>buff</x:v>
+      </x:c>
+      <x:c r="E36" s="47" t="str">
+        <x:v>self</x:v>
+      </x:c>
+      <x:c r="F36" s="47" t="str">
+        <x:v>flat</x:v>
+      </x:c>
+      <x:c r="G36" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H36" s="47" t="str">
+        <x:v>BUF</x:v>
+      </x:c>
+      <x:c r="I36" s="47" t="str">
+        <x:v>다음 공격 피해를 강화한다.</x:v>
+      </x:c>
+      <x:c r="J36" s="47"/>
+      <x:c r="K36" s="48"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1185,16 +2254,16 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="52" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="58" hidden="0" customWidth="1"/>
     <x:col min="1" max="1" width="4" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1340,7 +2409,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K5" s="46" t="str">
-        <x:v>인카운터 시작 시 공격 예고.</x:v>
+        <x:v>인카운터 시작 시 기본 공격 예고.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1358,144 +2427,950 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="45" t="str">
-        <x:v>mire_imp_guard</x:v>
+        <x:v>mire_imp_crouch</x:v>
       </x:c>
       <x:c r="G6" s="45" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H6" s="45" t="str">
-        <x:v>start</x:v>
+        <x:v>after_crouch</x:v>
       </x:c>
       <x:c r="I6" s="45"/>
       <x:c r="J6" s="45" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K6" s="46" t="str">
-        <x:v>휘두르기 이후 방어 예고.</x:v>
+        <x:v>공격 뒤 방어를 보여준다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="39"/>
       <x:c r="B7" s="49" t="str">
-        <x:v>frost_revenant_basic_start</x:v>
+        <x:v>mire_imp_basic_after_crouch</x:v>
       </x:c>
       <x:c r="C7" s="45" t="str">
-        <x:v>frost_revenant_basic</x:v>
+        <x:v>mire_imp_basic</x:v>
       </x:c>
       <x:c r="D7" s="45" t="str">
-        <x:v>start</x:v>
+        <x:v>after_crouch</x:v>
       </x:c>
       <x:c r="E7" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F7" s="45" t="str">
-        <x:v>frost_morale</x:v>
+        <x:v>mire_imp_flurry</x:v>
       </x:c>
       <x:c r="G7" s="45" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H7" s="45" t="str">
-        <x:v>after_morale</x:v>
+        <x:v>start</x:v>
       </x:c>
       <x:c r="I7" s="45"/>
       <x:c r="J7" s="45" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K7" s="46" t="str">
-        <x:v>인카운터 시작 시 사기 예고.</x:v>
+        <x:v>방어 뒤 약한 강공격.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="39"/>
       <x:c r="B8" s="49" t="str">
-        <x:v>frost_revenant_basic_after_morale</x:v>
+        <x:v>mire_imp_basic_giggle</x:v>
       </x:c>
       <x:c r="C8" s="45" t="str">
-        <x:v>frost_revenant_basic</x:v>
+        <x:v>mire_imp_basic</x:v>
       </x:c>
       <x:c r="D8" s="45" t="str">
-        <x:v>after_morale</x:v>
+        <x:v>giggle</x:v>
       </x:c>
       <x:c r="E8" s="45" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="45" t="str">
-        <x:v>frost_ice_blade</x:v>
+        <x:v>mire_imp_giggle</x:v>
       </x:c>
       <x:c r="G8" s="45" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H8" s="45" t="str">
-        <x:v>after_ice_blade</x:v>
+        <x:v>after_crouch</x:v>
       </x:c>
       <x:c r="I8" s="45"/>
       <x:c r="J8" s="45" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="46" t="str">
-        <x:v>사기 이후 얼음 칼날 예고.</x:v>
+        <x:v>HP 조건으로 끼어드는 템포 압박.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="39"/>
       <x:c r="B9" s="49" t="str">
-        <x:v>frost_revenant_basic_after_ice_blade</x:v>
+        <x:v>bog_stalker_basic_start</x:v>
       </x:c>
       <x:c r="C9" s="45" t="str">
-        <x:v>frost_revenant_basic</x:v>
+        <x:v>bog_stalker_basic</x:v>
       </x:c>
       <x:c r="D9" s="45" t="str">
-        <x:v>after_ice_blade</x:v>
+        <x:v>start</x:v>
       </x:c>
       <x:c r="E9" s="45" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="45" t="str">
-        <x:v>frost_ice_armor</x:v>
+        <x:v>bog_stalker_venom</x:v>
       </x:c>
       <x:c r="G9" s="45" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H9" s="45" t="str">
-        <x:v>after_ice_armor</x:v>
+        <x:v>after_venom</x:v>
       </x:c>
       <x:c r="I9" s="45"/>
       <x:c r="J9" s="45" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K9" s="46" t="str">
-        <x:v>얼음 칼날 이후 얼음 갑옷 예고.</x:v>
+        <x:v>첫 행동은 다음 공격 강화 전조.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="42"/>
-      <x:c r="B10" s="50" t="str">
+      <x:c r="A10" s="39"/>
+      <x:c r="B10" s="49" t="str">
+        <x:v>bog_stalker_basic_after_venom</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="str">
+        <x:v>bog_stalker_basic</x:v>
+      </x:c>
+      <x:c r="D10" s="45" t="str">
+        <x:v>after_venom</x:v>
+      </x:c>
+      <x:c r="E10" s="45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F10" s="45" t="str">
+        <x:v>bog_stalker_stab</x:v>
+      </x:c>
+      <x:c r="G10" s="45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H10" s="45" t="str">
+        <x:v>after_stab</x:v>
+      </x:c>
+      <x:c r="I10" s="45"/>
+      <x:c r="J10" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K10" s="46" t="str">
+        <x:v>짧은 카운트의 기본 공격.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="39"/>
+      <x:c r="B11" s="49" t="str">
+        <x:v>bog_stalker_basic_after_stab</x:v>
+      </x:c>
+      <x:c r="C11" s="45" t="str">
+        <x:v>bog_stalker_basic</x:v>
+      </x:c>
+      <x:c r="D11" s="45" t="str">
+        <x:v>after_stab</x:v>
+      </x:c>
+      <x:c r="E11" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F11" s="45" t="str">
+        <x:v>bog_stalker_ambush</x:v>
+      </x:c>
+      <x:c r="G11" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H11" s="45" t="str">
+        <x:v>after_ambush</x:v>
+      </x:c>
+      <x:c r="I11" s="45"/>
+      <x:c r="J11" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="46" t="str">
+        <x:v>템포 압박 공격.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="39"/>
+      <x:c r="B12" s="49" t="str">
+        <x:v>bog_stalker_basic_after_ambush</x:v>
+      </x:c>
+      <x:c r="C12" s="45" t="str">
+        <x:v>bog_stalker_basic</x:v>
+      </x:c>
+      <x:c r="D12" s="45" t="str">
+        <x:v>after_ambush</x:v>
+      </x:c>
+      <x:c r="E12" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F12" s="45" t="str">
+        <x:v>bog_stalker_mud_cover</x:v>
+      </x:c>
+      <x:c r="G12" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H12" s="45" t="str">
+        <x:v>after_venom</x:v>
+      </x:c>
+      <x:c r="I12" s="45"/>
+      <x:c r="J12" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="46" t="str">
+        <x:v>짧은 방어 후 다시 압박.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="39"/>
+      <x:c r="B13" s="49" t="str">
+        <x:v>bone_crawler_basic_start</x:v>
+      </x:c>
+      <x:c r="C13" s="45" t="str">
+        <x:v>bone_crawler_basic</x:v>
+      </x:c>
+      <x:c r="D13" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="E13" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="45" t="str">
+        <x:v>bone_crawler_skull_slam</x:v>
+      </x:c>
+      <x:c r="G13" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H13" s="45" t="str">
+        <x:v>after_slam</x:v>
+      </x:c>
+      <x:c r="I13" s="45"/>
+      <x:c r="J13" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="46" t="str">
+        <x:v>강한 선공 예고.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="39"/>
+      <x:c r="B14" s="49" t="str">
+        <x:v>bone_crawler_basic_after_slam</x:v>
+      </x:c>
+      <x:c r="C14" s="45" t="str">
+        <x:v>bone_crawler_basic</x:v>
+      </x:c>
+      <x:c r="D14" s="45" t="str">
+        <x:v>after_slam</x:v>
+      </x:c>
+      <x:c r="E14" s="45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F14" s="45" t="str">
+        <x:v>bone_crawler_reassemble</x:v>
+      </x:c>
+      <x:c r="G14" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H14" s="45" t="str">
+        <x:v>after_reassemble</x:v>
+      </x:c>
+      <x:c r="I14" s="45"/>
+      <x:c r="J14" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="46" t="str">
+        <x:v>강공격 뒤 빈틈.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="39"/>
+      <x:c r="B15" s="49" t="str">
+        <x:v>bone_crawler_basic_after_reassemble</x:v>
+      </x:c>
+      <x:c r="C15" s="45" t="str">
+        <x:v>bone_crawler_basic</x:v>
+      </x:c>
+      <x:c r="D15" s="45" t="str">
+        <x:v>after_reassemble</x:v>
+      </x:c>
+      <x:c r="E15" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F15" s="45" t="str">
+        <x:v>bone_crawler_claw</x:v>
+      </x:c>
+      <x:c r="G15" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H15" s="45" t="str">
+        <x:v>after_claw</x:v>
+      </x:c>
+      <x:c r="I15" s="45"/>
+      <x:c r="J15" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K15" s="46" t="str">
+        <x:v>기본 공격.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="39"/>
+      <x:c r="B16" s="49" t="str">
+        <x:v>bone_crawler_basic_after_claw</x:v>
+      </x:c>
+      <x:c r="C16" s="45" t="str">
+        <x:v>bone_crawler_basic</x:v>
+      </x:c>
+      <x:c r="D16" s="45" t="str">
+        <x:v>after_claw</x:v>
+      </x:c>
+      <x:c r="E16" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F16" s="45" t="str">
+        <x:v>bone_crawler_cracked_bone</x:v>
+      </x:c>
+      <x:c r="G16" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H16" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="I16" s="45"/>
+      <x:c r="J16" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K16" s="46" t="str">
+        <x:v>다음 강공격 전 정비.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="39"/>
+      <x:c r="B17" s="49" t="str">
+        <x:v>gravebound_crawler_basic_start</x:v>
+      </x:c>
+      <x:c r="C17" s="45" t="str">
+        <x:v>gravebound_crawler_basic</x:v>
+      </x:c>
+      <x:c r="D17" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="E17" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" s="45" t="str">
+        <x:v>gravebound_earth_armor</x:v>
+      </x:c>
+      <x:c r="G17" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H17" s="45" t="str">
+        <x:v>after_armor</x:v>
+      </x:c>
+      <x:c r="I17" s="45"/>
+      <x:c r="J17" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K17" s="46" t="str">
+        <x:v>장기전 방어 시작.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="39"/>
+      <x:c r="B18" s="49" t="str">
+        <x:v>gravebound_crawler_basic_after_armor</x:v>
+      </x:c>
+      <x:c r="C18" s="45" t="str">
+        <x:v>gravebound_crawler_basic</x:v>
+      </x:c>
+      <x:c r="D18" s="45" t="str">
+        <x:v>after_armor</x:v>
+      </x:c>
+      <x:c r="E18" s="45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F18" s="45" t="str">
+        <x:v>gravebound_bite</x:v>
+      </x:c>
+      <x:c r="G18" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H18" s="45" t="str">
+        <x:v>after_bite</x:v>
+      </x:c>
+      <x:c r="I18" s="45"/>
+      <x:c r="J18" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K18" s="46" t="str">
+        <x:v>기본 공격.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="39"/>
+      <x:c r="B19" s="49" t="str">
+        <x:v>gravebound_crawler_basic_after_bite</x:v>
+      </x:c>
+      <x:c r="C19" s="45" t="str">
+        <x:v>gravebound_crawler_basic</x:v>
+      </x:c>
+      <x:c r="D19" s="45" t="str">
+        <x:v>after_bite</x:v>
+      </x:c>
+      <x:c r="E19" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F19" s="45" t="str">
+        <x:v>gravebound_hard_bones</x:v>
+      </x:c>
+      <x:c r="G19" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H19" s="45" t="str">
+        <x:v>after_hard_bones</x:v>
+      </x:c>
+      <x:c r="I19" s="45"/>
+      <x:c r="J19" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K19" s="46" t="str">
+        <x:v>방어 돌파를 요구하는 정비 턴.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="39"/>
+      <x:c r="B20" s="49" t="str">
+        <x:v>gravebound_crawler_basic_after_hard_bones</x:v>
+      </x:c>
+      <x:c r="C20" s="45" t="str">
+        <x:v>gravebound_crawler_basic</x:v>
+      </x:c>
+      <x:c r="D20" s="45" t="str">
+        <x:v>after_hard_bones</x:v>
+      </x:c>
+      <x:c r="E20" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F20" s="45" t="str">
+        <x:v>gravebound_jaw</x:v>
+      </x:c>
+      <x:c r="G20" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H20" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="I20" s="45"/>
+      <x:c r="J20" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K20" s="46" t="str">
+        <x:v>방어 누적 후 위협 공격.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="39"/>
+      <x:c r="B21" s="49" t="str">
+        <x:v>frost_revenant_basic_start</x:v>
+      </x:c>
+      <x:c r="C21" s="45" t="str">
+        <x:v>frost_revenant_basic</x:v>
+      </x:c>
+      <x:c r="D21" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="E21" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F21" s="45" t="str">
+        <x:v>frost_morale</x:v>
+      </x:c>
+      <x:c r="G21" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H21" s="45" t="str">
+        <x:v>after_morale</x:v>
+      </x:c>
+      <x:c r="I21" s="45"/>
+      <x:c r="J21" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K21" s="46" t="str">
+        <x:v>인카운터 시작 시 사기 예고.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="39"/>
+      <x:c r="B22" s="49" t="str">
+        <x:v>frost_revenant_basic_after_morale</x:v>
+      </x:c>
+      <x:c r="C22" s="45" t="str">
+        <x:v>frost_revenant_basic</x:v>
+      </x:c>
+      <x:c r="D22" s="45" t="str">
+        <x:v>after_morale</x:v>
+      </x:c>
+      <x:c r="E22" s="45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F22" s="45" t="str">
+        <x:v>frost_ice_blade</x:v>
+      </x:c>
+      <x:c r="G22" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H22" s="45" t="str">
+        <x:v>after_ice_blade</x:v>
+      </x:c>
+      <x:c r="I22" s="45"/>
+      <x:c r="J22" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K22" s="46" t="str">
+        <x:v>사기 이후 얼음 칼날.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="39"/>
+      <x:c r="B23" s="49" t="str">
+        <x:v>frost_revenant_basic_after_ice_blade</x:v>
+      </x:c>
+      <x:c r="C23" s="45" t="str">
+        <x:v>frost_revenant_basic</x:v>
+      </x:c>
+      <x:c r="D23" s="45" t="str">
+        <x:v>after_ice_blade</x:v>
+      </x:c>
+      <x:c r="E23" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F23" s="45" t="str">
+        <x:v>frost_ice_armor</x:v>
+      </x:c>
+      <x:c r="G23" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H23" s="45" t="str">
+        <x:v>after_ice_armor</x:v>
+      </x:c>
+      <x:c r="I23" s="45"/>
+      <x:c r="J23" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K23" s="46" t="str">
+        <x:v>공격 후 방어 턴.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="39"/>
+      <x:c r="B24" s="49" t="str">
         <x:v>frost_revenant_basic_after_ice_armor</x:v>
       </x:c>
-      <x:c r="C10" s="47" t="str">
+      <x:c r="C24" s="45" t="str">
         <x:v>frost_revenant_basic</x:v>
       </x:c>
-      <x:c r="D10" s="47" t="str">
+      <x:c r="D24" s="45" t="str">
         <x:v>after_ice_armor</x:v>
       </x:c>
-      <x:c r="E10" s="47" t="n">
+      <x:c r="E24" s="45" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F10" s="47" t="str">
-        <x:v>frost_ice_blade</x:v>
-      </x:c>
-      <x:c r="G10" s="47" t="n">
+      <x:c r="F24" s="45" t="str">
+        <x:v>frost_cleave</x:v>
+      </x:c>
+      <x:c r="G24" s="45" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H10" s="47" t="str">
-        <x:v>after_ice_blade</x:v>
-      </x:c>
-      <x:c r="I10" s="47"/>
-      <x:c r="J10" s="47" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K10" s="48" t="str">
-        <x:v>얼음 갑옷 이후 다시 얼음 칼날로 반복.</x:v>
+      <x:c r="H24" s="45" t="str">
+        <x:v>after_cleave</x:v>
+      </x:c>
+      <x:c r="I24" s="45"/>
+      <x:c r="J24" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K24" s="46" t="str">
+        <x:v>강한 공격 압박.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="39"/>
+      <x:c r="B25" s="49" t="str">
+        <x:v>frost_revenant_basic_after_cleave</x:v>
+      </x:c>
+      <x:c r="C25" s="45" t="str">
+        <x:v>frost_revenant_basic</x:v>
+      </x:c>
+      <x:c r="D25" s="45" t="str">
+        <x:v>after_cleave</x:v>
+      </x:c>
+      <x:c r="E25" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F25" s="45" t="str">
+        <x:v>frost_mark</x:v>
+      </x:c>
+      <x:c r="G25" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H25" s="45" t="str">
+        <x:v>after_morale</x:v>
+      </x:c>
+      <x:c r="I25" s="45"/>
+      <x:c r="J25" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K25" s="46" t="str">
+        <x:v>엘리트 특수 행동.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="39"/>
+      <x:c r="B26" s="49" t="str">
+        <x:v>crown_acolyte_basic_start</x:v>
+      </x:c>
+      <x:c r="C26" s="45" t="str">
+        <x:v>crown_acolyte_basic</x:v>
+      </x:c>
+      <x:c r="D26" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="E26" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F26" s="45" t="str">
+        <x:v>crown_sentence</x:v>
+      </x:c>
+      <x:c r="G26" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H26" s="45" t="str">
+        <x:v>after_sentence</x:v>
+      </x:c>
+      <x:c r="I26" s="45"/>
+      <x:c r="J26" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K26" s="46" t="str">
+        <x:v>심판 전조.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="39"/>
+      <x:c r="B27" s="49" t="str">
+        <x:v>crown_acolyte_basic_after_sentence</x:v>
+      </x:c>
+      <x:c r="C27" s="45" t="str">
+        <x:v>crown_acolyte_basic</x:v>
+      </x:c>
+      <x:c r="D27" s="45" t="str">
+        <x:v>after_sentence</x:v>
+      </x:c>
+      <x:c r="E27" s="45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F27" s="45" t="str">
+        <x:v>crown_staff</x:v>
+      </x:c>
+      <x:c r="G27" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H27" s="45" t="str">
+        <x:v>after_staff</x:v>
+      </x:c>
+      <x:c r="I27" s="45"/>
+      <x:c r="J27" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K27" s="46" t="str">
+        <x:v>빠른 강공격.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="39"/>
+      <x:c r="B28" s="49" t="str">
+        <x:v>crown_acolyte_basic_after_staff</x:v>
+      </x:c>
+      <x:c r="C28" s="45" t="str">
+        <x:v>crown_acolyte_basic</x:v>
+      </x:c>
+      <x:c r="D28" s="45" t="str">
+        <x:v>after_staff</x:v>
+      </x:c>
+      <x:c r="E28" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F28" s="45" t="str">
+        <x:v>crown_deep_faith</x:v>
+      </x:c>
+      <x:c r="G28" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H28" s="45" t="str">
+        <x:v>after_deep_faith</x:v>
+      </x:c>
+      <x:c r="I28" s="45"/>
+      <x:c r="J28" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K28" s="46" t="str">
+        <x:v>다음 공격 강화.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="39"/>
+      <x:c r="B29" s="49" t="str">
+        <x:v>crown_acolyte_basic_after_deep_faith</x:v>
+      </x:c>
+      <x:c r="C29" s="45" t="str">
+        <x:v>crown_acolyte_basic</x:v>
+      </x:c>
+      <x:c r="D29" s="45" t="str">
+        <x:v>after_deep_faith</x:v>
+      </x:c>
+      <x:c r="E29" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F29" s="45" t="str">
+        <x:v>crown_judgement</x:v>
+      </x:c>
+      <x:c r="G29" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H29" s="45" t="str">
+        <x:v>after_judgement</x:v>
+      </x:c>
+      <x:c r="I29" s="45"/>
+      <x:c r="J29" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K29" s="46" t="str">
+        <x:v>큰 위험 턴.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="39"/>
+      <x:c r="B30" s="49" t="str">
+        <x:v>crown_acolyte_basic_after_judgement</x:v>
+      </x:c>
+      <x:c r="C30" s="45" t="str">
+        <x:v>crown_acolyte_basic</x:v>
+      </x:c>
+      <x:c r="D30" s="45" t="str">
+        <x:v>after_judgement</x:v>
+      </x:c>
+      <x:c r="E30" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F30" s="45" t="str">
+        <x:v>crown_veil</x:v>
+      </x:c>
+      <x:c r="G30" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H30" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="I30" s="45"/>
+      <x:c r="J30" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K30" s="46" t="str">
+        <x:v>강공격 후 방어.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="39"/>
+      <x:c r="B31" s="49" t="str">
+        <x:v>abyssal_crown_guardian_basic_start</x:v>
+      </x:c>
+      <x:c r="C31" s="45" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="D31" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="E31" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F31" s="45" t="str">
+        <x:v>guardian_sentence</x:v>
+      </x:c>
+      <x:c r="G31" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H31" s="45" t="str">
+        <x:v>after_sentence</x:v>
+      </x:c>
+      <x:c r="I31" s="45"/>
+      <x:c r="J31" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K31" s="46" t="str">
+        <x:v>보스 큰 패턴 전조.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="39"/>
+      <x:c r="B32" s="49" t="str">
+        <x:v>abyssal_crown_guardian_basic_after_sentence</x:v>
+      </x:c>
+      <x:c r="C32" s="45" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="D32" s="45" t="str">
+        <x:v>after_sentence</x:v>
+      </x:c>
+      <x:c r="E32" s="45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F32" s="45" t="str">
+        <x:v>guardian_crush</x:v>
+      </x:c>
+      <x:c r="G32" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H32" s="45" t="str">
+        <x:v>after_crush</x:v>
+      </x:c>
+      <x:c r="I32" s="45"/>
+      <x:c r="J32" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K32" s="46" t="str">
+        <x:v>기본 보스 강공격.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="39"/>
+      <x:c r="B33" s="49" t="str">
+        <x:v>abyssal_crown_guardian_basic_after_crush</x:v>
+      </x:c>
+      <x:c r="C33" s="45" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="D33" s="45" t="str">
+        <x:v>after_crush</x:v>
+      </x:c>
+      <x:c r="E33" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F33" s="45" t="str">
+        <x:v>guardian_barrier</x:v>
+      </x:c>
+      <x:c r="G33" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H33" s="45" t="str">
+        <x:v>after_barrier</x:v>
+      </x:c>
+      <x:c r="I33" s="45"/>
+      <x:c r="J33" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K33" s="46" t="str">
+        <x:v>방어 턴.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="39"/>
+      <x:c r="B34" s="49" t="str">
+        <x:v>abyssal_crown_guardian_basic_after_barrier</x:v>
+      </x:c>
+      <x:c r="C34" s="45" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="D34" s="45" t="str">
+        <x:v>after_barrier</x:v>
+      </x:c>
+      <x:c r="E34" s="45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F34" s="45" t="str">
+        <x:v>guardian_authority</x:v>
+      </x:c>
+      <x:c r="G34" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H34" s="45" t="str">
+        <x:v>after_authority</x:v>
+      </x:c>
+      <x:c r="I34" s="45"/>
+      <x:c r="J34" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K34" s="46" t="str">
+        <x:v>다음 공격 강화.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="39"/>
+      <x:c r="B35" s="49" t="str">
+        <x:v>abyssal_crown_guardian_basic_after_authority</x:v>
+      </x:c>
+      <x:c r="C35" s="45" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="D35" s="45" t="str">
+        <x:v>after_authority</x:v>
+      </x:c>
+      <x:c r="E35" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F35" s="45" t="str">
+        <x:v>guardian_edict</x:v>
+      </x:c>
+      <x:c r="G35" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H35" s="45" t="str">
+        <x:v>after_edict</x:v>
+      </x:c>
+      <x:c r="I35" s="45"/>
+      <x:c r="J35" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K35" s="46" t="str">
+        <x:v>보스 피니셔.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="42"/>
+      <x:c r="B36" s="50" t="str">
+        <x:v>abyssal_crown_guardian_basic_after_edict</x:v>
+      </x:c>
+      <x:c r="C36" s="47" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="D36" s="47" t="str">
+        <x:v>after_edict</x:v>
+      </x:c>
+      <x:c r="E36" s="47" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F36" s="47" t="str">
+        <x:v>guardian_deep_guard</x:v>
+      </x:c>
+      <x:c r="G36" s="47" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H36" s="47" t="str">
+        <x:v>after_sentence</x:v>
+      </x:c>
+      <x:c r="I36" s="47"/>
+      <x:c r="J36" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K36" s="48" t="str">
+        <x:v>큰 공격 후 수호.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1507,19 +3382,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="52" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="58" hidden="0" customWidth="1"/>
     <x:col min="1" max="1" width="4" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1828,43 +3703,283 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="42"/>
-      <x:c r="B9" s="50" t="str">
+      <x:c r="A9" s="39"/>
+      <x:c r="B9" s="49" t="str">
+        <x:v>enc_bog_stalker_2_enemy_1</x:v>
+      </x:c>
+      <x:c r="C9" s="45" t="str">
+        <x:v>enc_bog_stalker_2</x:v>
+      </x:c>
+      <x:c r="D9" s="45" t="str">
+        <x:v>enemy_1</x:v>
+      </x:c>
+      <x:c r="E9" s="45" t="str">
+        <x:v>bog_stalker</x:v>
+      </x:c>
+      <x:c r="F9" s="45" t="str">
+        <x:v>bog_stalker_basic</x:v>
+      </x:c>
+      <x:c r="G9" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="H9" s="45"/>
+      <x:c r="I9" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L9" s="45" t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c r="M9" s="45" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="N9" s="46" t="str">
+        <x:v>늪독 예고.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="39"/>
+      <x:c r="B10" s="49" t="str">
+        <x:v>enc_bog_stalker_2_enemy_2</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="str">
+        <x:v>enc_bog_stalker_2</x:v>
+      </x:c>
+      <x:c r="D10" s="45" t="str">
+        <x:v>enemy_2</x:v>
+      </x:c>
+      <x:c r="E10" s="45" t="str">
+        <x:v>bog_stalker</x:v>
+      </x:c>
+      <x:c r="F10" s="45" t="str">
+        <x:v>bog_stalker_basic</x:v>
+      </x:c>
+      <x:c r="G10" s="45" t="str">
+        <x:v>after_venom</x:v>
+      </x:c>
+      <x:c r="H10" s="45"/>
+      <x:c r="I10" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K10" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L10" s="45" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="M10" s="45" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="N10" s="46" t="str">
+        <x:v>찌르기 예고.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="39"/>
+      <x:c r="B11" s="49" t="str">
+        <x:v>enc_gravebound_crawler_2_enemy_1</x:v>
+      </x:c>
+      <x:c r="C11" s="45" t="str">
+        <x:v>enc_gravebound_crawler_2</x:v>
+      </x:c>
+      <x:c r="D11" s="45" t="str">
+        <x:v>enemy_1</x:v>
+      </x:c>
+      <x:c r="E11" s="45" t="str">
+        <x:v>gravebound_crawler</x:v>
+      </x:c>
+      <x:c r="F11" s="45" t="str">
+        <x:v>gravebound_crawler_basic</x:v>
+      </x:c>
+      <x:c r="G11" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="H11" s="45"/>
+      <x:c r="I11" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L11" s="45" t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c r="M11" s="45" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="N11" s="46" t="str">
+        <x:v>방어 시작.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="39"/>
+      <x:c r="B12" s="49" t="str">
+        <x:v>enc_gravebound_crawler_2_enemy_2</x:v>
+      </x:c>
+      <x:c r="C12" s="45" t="str">
+        <x:v>enc_gravebound_crawler_2</x:v>
+      </x:c>
+      <x:c r="D12" s="45" t="str">
+        <x:v>enemy_2</x:v>
+      </x:c>
+      <x:c r="E12" s="45" t="str">
+        <x:v>gravebound_crawler</x:v>
+      </x:c>
+      <x:c r="F12" s="45" t="str">
+        <x:v>gravebound_crawler_basic</x:v>
+      </x:c>
+      <x:c r="G12" s="45" t="str">
+        <x:v>after_armor</x:v>
+      </x:c>
+      <x:c r="H12" s="45"/>
+      <x:c r="I12" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L12" s="45" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="M12" s="45" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="N12" s="46" t="str">
+        <x:v>공격 시작.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="39"/>
+      <x:c r="B13" s="49" t="str">
         <x:v>enc_frost_revenant_1_enemy_1</x:v>
       </x:c>
-      <x:c r="C9" s="47" t="str">
+      <x:c r="C13" s="45" t="str">
         <x:v>enc_frost_revenant_1</x:v>
       </x:c>
-      <x:c r="D9" s="47" t="str">
+      <x:c r="D13" s="45" t="str">
         <x:v>enemy_1</x:v>
       </x:c>
-      <x:c r="E9" s="47" t="str">
+      <x:c r="E13" s="45" t="str">
         <x:v>frost_revenant</x:v>
       </x:c>
-      <x:c r="F9" s="47" t="str">
+      <x:c r="F13" s="45" t="str">
         <x:v>frost_revenant_basic</x:v>
       </x:c>
-      <x:c r="G9" s="47" t="str">
+      <x:c r="G13" s="45" t="str">
         <x:v>start</x:v>
       </x:c>
-      <x:c r="H9" s="47"/>
-      <x:c r="I9" s="47" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J9" s="47" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K9" s="47" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L9" s="47" t="n">
+      <x:c r="H13" s="45"/>
+      <x:c r="I13" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L13" s="45" t="n">
         <x:v>980</x:v>
       </x:c>
-      <x:c r="M9" s="47" t="n">
+      <x:c r="M13" s="45" t="n">
         <x:v>410</x:v>
       </x:c>
-      <x:c r="N9" s="48" t="str">
+      <x:c r="N13" s="46" t="str">
         <x:v>사기 예고로 시작.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="39"/>
+      <x:c r="B14" s="49" t="str">
+        <x:v>enc_crown_acolyte_1_enemy_1</x:v>
+      </x:c>
+      <x:c r="C14" s="45" t="str">
+        <x:v>enc_crown_acolyte_1</x:v>
+      </x:c>
+      <x:c r="D14" s="45" t="str">
+        <x:v>enemy_1</x:v>
+      </x:c>
+      <x:c r="E14" s="45" t="str">
+        <x:v>crown_acolyte</x:v>
+      </x:c>
+      <x:c r="F14" s="45" t="str">
+        <x:v>crown_acolyte_basic</x:v>
+      </x:c>
+      <x:c r="G14" s="45" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="H14" s="45"/>
+      <x:c r="I14" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L14" s="45" t="n">
+        <x:v>980</x:v>
+      </x:c>
+      <x:c r="M14" s="45" t="n">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N14" s="46" t="str">
+        <x:v>단죄 선포로 시작.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="42"/>
+      <x:c r="B15" s="50" t="str">
+        <x:v>enc_abyssal_crown_guardian_1_enemy_1</x:v>
+      </x:c>
+      <x:c r="C15" s="47" t="str">
+        <x:v>enc_abyssal_crown_guardian_1</x:v>
+      </x:c>
+      <x:c r="D15" s="47" t="str">
+        <x:v>enemy_1</x:v>
+      </x:c>
+      <x:c r="E15" s="47" t="str">
+        <x:v>abyssal_crown_guardian</x:v>
+      </x:c>
+      <x:c r="F15" s="47" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="G15" s="47" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="H15" s="47"/>
+      <x:c r="I15" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K15" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L15" s="47" t="n">
+        <x:v>980</x:v>
+      </x:c>
+      <x:c r="M15" s="47" t="n">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N15" s="48" t="str">
+        <x:v>심연 선고로 시작.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1876,17 +3991,17 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="10" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="56" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="62" hidden="0" customWidth="1"/>
     <x:col min="1" max="1" width="4" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -2015,37 +4130,261 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="42"/>
-      <x:c r="B5" s="50" t="str">
+      <x:c r="A5" s="39"/>
+      <x:c r="B5" s="49" t="str">
+        <x:v>mire_imp_hp50_giggle</x:v>
+      </x:c>
+      <x:c r="C5" s="45" t="str">
+        <x:v>mire_imp</x:v>
+      </x:c>
+      <x:c r="D5" s="45" t="str">
+        <x:v>mire_imp_basic</x:v>
+      </x:c>
+      <x:c r="E5" s="45" t="str">
+        <x:v>hp_below</x:v>
+      </x:c>
+      <x:c r="F5" s="45" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G5" s="58" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I5" s="45"/>
+      <x:c r="J5" s="45" t="str">
+        <x:v>giggle</x:v>
+      </x:c>
+      <x:c r="K5" s="45"/>
+      <x:c r="L5" s="46" t="str">
+        <x:v>HP 50% 이하가 되면 낄낄대기로 템포 압박.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="39"/>
+      <x:c r="B6" s="49" t="str">
+        <x:v>bog_stalker_hp40_cover</x:v>
+      </x:c>
+      <x:c r="C6" s="45" t="str">
+        <x:v>bog_stalker</x:v>
+      </x:c>
+      <x:c r="D6" s="45" t="str">
+        <x:v>bog_stalker_basic</x:v>
+      </x:c>
+      <x:c r="E6" s="45" t="str">
+        <x:v>hp_below</x:v>
+      </x:c>
+      <x:c r="F6" s="45" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G6" s="58" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I6" s="45"/>
+      <x:c r="J6" s="45" t="str">
+        <x:v>after_ambush</x:v>
+      </x:c>
+      <x:c r="K6" s="45"/>
+      <x:c r="L6" s="46" t="str">
+        <x:v>HP 40% 이하에서 진흙 엄폐 후 기습 루프로 전환.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="39"/>
+      <x:c r="B7" s="49" t="str">
+        <x:v>bone_crawler_hp60_crack</x:v>
+      </x:c>
+      <x:c r="C7" s="45" t="str">
+        <x:v>bone_crawler</x:v>
+      </x:c>
+      <x:c r="D7" s="45" t="str">
+        <x:v>bone_crawler_basic</x:v>
+      </x:c>
+      <x:c r="E7" s="45" t="str">
+        <x:v>hp_below</x:v>
+      </x:c>
+      <x:c r="F7" s="45" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G7" s="58" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I7" s="45"/>
+      <x:c r="J7" s="45" t="str">
+        <x:v>after_claw</x:v>
+      </x:c>
+      <x:c r="K7" s="45"/>
+      <x:c r="L7" s="46" t="str">
+        <x:v>HP 60% 이하에서 금 간 뼈로 정비.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="39"/>
+      <x:c r="B8" s="49" t="str">
+        <x:v>gravebound_hp35_hard_bones</x:v>
+      </x:c>
+      <x:c r="C8" s="45" t="str">
+        <x:v>gravebound_crawler</x:v>
+      </x:c>
+      <x:c r="D8" s="45" t="str">
+        <x:v>gravebound_crawler_basic</x:v>
+      </x:c>
+      <x:c r="E8" s="45" t="str">
+        <x:v>hp_below</x:v>
+      </x:c>
+      <x:c r="F8" s="45" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G8" s="58" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I8" s="45"/>
+      <x:c r="J8" s="45" t="str">
+        <x:v>after_bite</x:v>
+      </x:c>
+      <x:c r="K8" s="45"/>
+      <x:c r="L8" s="46" t="str">
+        <x:v>HP 35% 이하에서 망자의 강골 우선.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="39"/>
+      <x:c r="B9" s="49" t="str">
         <x:v>frost_hp50_armor</x:v>
       </x:c>
-      <x:c r="C5" s="47" t="str">
+      <x:c r="C9" s="45" t="str">
         <x:v>frost_revenant</x:v>
       </x:c>
-      <x:c r="D5" s="47" t="str">
+      <x:c r="D9" s="45" t="str">
         <x:v>frost_revenant_basic</x:v>
       </x:c>
-      <x:c r="E5" s="47" t="str">
+      <x:c r="E9" s="45" t="str">
         <x:v>hp_below</x:v>
       </x:c>
-      <x:c r="F5" s="47" t="n">
+      <x:c r="F9" s="45" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G5" s="55" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="47" t="n">
+      <x:c r="G9" s="58" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="45" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="I5" s="47"/>
-      <x:c r="J5" s="47" t="str">
+      <x:c r="I9" s="45"/>
+      <x:c r="J9" s="45" t="str">
         <x:v>after_ice_blade</x:v>
       </x:c>
-      <x:c r="K5" s="47" t="n">
+      <x:c r="K9" s="45" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L5" s="48" t="str">
-        <x:v>HP 50% 이하가 되면 다음 행동을 빠른 얼음 갑옷으로 전환하는 예시.</x:v>
+      <x:c r="L9" s="46" t="str">
+        <x:v>HP 50% 이하가 되면 빠른 얼음 갑옷.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="39"/>
+      <x:c r="B10" s="49" t="str">
+        <x:v>crown_hp30_deep_faith</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="str">
+        <x:v>crown_acolyte</x:v>
+      </x:c>
+      <x:c r="D10" s="45" t="str">
+        <x:v>crown_acolyte_basic</x:v>
+      </x:c>
+      <x:c r="E10" s="45" t="str">
+        <x:v>hp_below</x:v>
+      </x:c>
+      <x:c r="F10" s="45" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="58" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="45" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I10" s="45"/>
+      <x:c r="J10" s="45" t="str">
+        <x:v>after_staff</x:v>
+      </x:c>
+      <x:c r="K10" s="45"/>
+      <x:c r="L10" s="46" t="str">
+        <x:v>HP 30% 이하에서 깊은 신앙으로 강화.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="39"/>
+      <x:c r="B11" s="49" t="str">
+        <x:v>guardian_hp70_authority</x:v>
+      </x:c>
+      <x:c r="C11" s="45" t="str">
+        <x:v>abyssal_crown_guardian</x:v>
+      </x:c>
+      <x:c r="D11" s="45" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="E11" s="45" t="str">
+        <x:v>hp_below</x:v>
+      </x:c>
+      <x:c r="F11" s="45" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G11" s="58" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="45" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I11" s="45"/>
+      <x:c r="J11" s="45" t="str">
+        <x:v>after_barrier</x:v>
+      </x:c>
+      <x:c r="K11" s="45"/>
+      <x:c r="L11" s="46" t="str">
+        <x:v>HP 70% 이하에서 왕관의 권능으로 전환.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="42"/>
+      <x:c r="B12" s="50" t="str">
+        <x:v>guardian_hp40_sentence</x:v>
+      </x:c>
+      <x:c r="C12" s="47" t="str">
+        <x:v>abyssal_crown_guardian</x:v>
+      </x:c>
+      <x:c r="D12" s="47" t="str">
+        <x:v>abyssal_crown_guardian_basic</x:v>
+      </x:c>
+      <x:c r="E12" s="47" t="str">
+        <x:v>hp_below</x:v>
+      </x:c>
+      <x:c r="F12" s="47" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G12" s="59" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="47" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I12" s="47"/>
+      <x:c r="J12" s="47" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="K12" s="47"/>
+      <x:c r="L12" s="48" t="str">
+        <x:v>HP 40% 이하에서 심연 선고 루프로 복귀.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
